--- a/astro-site/public/dl/kit-tareas/BONUS-01-briefing-servicio.xlsx
+++ b/astro-site/public/dl/kit-tareas/BONUS-01-briefing-servicio.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Briefing" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Briefing" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -96,7 +96,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -118,27 +118,61 @@
         <color rgb="00E0E0E0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="2" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="3" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="12">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -498,15 +532,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B10"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -514,6 +549,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -521,9 +557,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" t="inlineStr"/>
-    </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -545,9 +579,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" t="inlineStr"/>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
         <is>
@@ -555,8 +587,25 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -565,14 +614,14 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:C37"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="30"/>
-    <col customWidth="1" max="3" min="3" width="50"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -589,13 +638,14 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="6" t="inlineStr">
         <is>
           <t>RESERVAS Y OCUPACIÓN</t>
         </is>
       </c>
-      <c r="C4" s="7" t="n"/>
+      <c r="C4" s="11" t="n"/>
     </row>
     <row r="5">
       <c r="B5" s="8" t="inlineStr">
@@ -641,13 +691,14 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="6" t="inlineStr">
         <is>
           <t>PLATOS DEL DÍA Y 86s</t>
         </is>
       </c>
-      <c r="C11" s="7" t="n"/>
+      <c r="C11" s="11" t="n"/>
     </row>
     <row r="12">
       <c r="B12" s="8" t="inlineStr">
@@ -689,13 +740,14 @@
       </c>
       <c r="C16" s="9" t="inlineStr"/>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
           <t>ALÉRGENOS Y ESPECIALES</t>
         </is>
       </c>
-      <c r="C18" s="7" t="n"/>
+      <c r="C18" s="11" t="n"/>
     </row>
     <row r="19">
       <c r="B19" s="8" t="inlineStr">
@@ -721,13 +773,14 @@
       </c>
       <c r="C21" s="9" t="inlineStr"/>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="B23" s="6" t="inlineStr">
         <is>
           <t>EQUIPO DEL TURNO</t>
         </is>
       </c>
-      <c r="C23" s="7" t="n"/>
+      <c r="C23" s="11" t="n"/>
     </row>
     <row r="24">
       <c r="B24" s="8" t="inlineStr">
@@ -761,13 +814,14 @@
       </c>
       <c r="C27" s="9" t="inlineStr"/>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="B29" s="6" t="inlineStr">
         <is>
           <t>NOTAS E INCIDENCIAS</t>
         </is>
       </c>
-      <c r="C29" s="7" t="n"/>
+      <c r="C29" s="11" t="n"/>
     </row>
     <row r="30">
       <c r="B30" s="8" t="inlineStr">
@@ -793,6 +847,8 @@
       </c>
       <c r="C32" s="9" t="inlineStr"/>
     </row>
+    <row r="33"/>
+    <row r="34"/>
     <row r="35">
       <c r="B35" s="5" t="inlineStr">
         <is>
@@ -800,6 +856,7 @@
         </is>
       </c>
     </row>
+    <row r="36"/>
     <row r="37">
       <c r="B37" s="10" t="inlineStr">
         <is>
@@ -816,7 +873,15 @@
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="B18:C18"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup orientation="portrait"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas/BONUS-01-briefing-servicio.xlsx
+++ b/astro-site/public/dl/kit-tareas/BONUS-01-briefing-servicio.xlsx
@@ -10,7 +10,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Briefing" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$B$23</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Briefing'!$A$1:$C$37</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -18,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -75,8 +78,22 @@
       <color rgb="00999999"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFD700"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00555555"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -93,6 +110,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E8F5E9"/>
         <bgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -155,7 +177,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -168,6 +190,18 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -534,64 +568,120 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1"/>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>BONUS: Plantilla de Briefing Pre-Servicio</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4">
-      <c r="B4" s="2" t="inlineStr">
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>Cómo usar esta plantilla</t>
         </is>
       </c>
     </row>
     <row r="5"/>
-    <row r="6">
-      <c r="B6" s="3" t="inlineStr">
+    <row r="6" ht="16" customHeight="1">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>▸ El jefe de sala o manager rellena antes del briefing</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="3" t="inlineStr">
+    <row r="7" ht="16" customHeight="1">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>▸ Se comunica al equipo en la reunión de 5-10 minutos pre-servicio</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" s="3" t="inlineStr">
+    <row r="8" ht="16" customHeight="1">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>▸ Imprime y pega en la zona de pase para referencia durante servicio</t>
         </is>
       </c>
     </row>
     <row r="9"/>
-    <row r="10">
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes · AI Chef Pro · aichef.pro</t>
+    <row r="10" ht="18" customHeight="1">
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Se conecta con</t>
         </is>
       </c>
     </row>
     <row r="11"/>
-    <row r="12">
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas · info@aichef.pro</t>
+    <row r="12" ht="32" customHeight="1">
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día (accesos, luces, clima, terraza).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>▸ 01-apertura-cierre.xlsx — el mismo día con el DETALLE por área (cocina, sala, barra).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>▸ 09-apertura-cierre-caja.xlsx — la CAJA: fondo, recuento por denominaciones, Z del TPV y descuadre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>▸ Orden de uso: local → áreas → caja. No se duplican: cada uno cubre un nivel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>▸ Estás en BONUS-01-briefing-servicio.xlsx: el briefing abre el turno que luego se trabaja con 01-apertura-cierre.xlsx y 06-eventos-festivos.xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Restaurante Casual · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="35" customHeight="1">
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>Contacto: info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -616,12 +706,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -653,7 +744,7 @@
           <t>Nº de reservas:</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr"/>
+      <c r="C5" s="15" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="B6" s="8" t="inlineStr">
@@ -661,7 +752,7 @@
           <t>Nº de comensales previstos:</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr"/>
+      <c r="C6" s="15" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" s="8" t="inlineStr">
@@ -669,7 +760,7 @@
           <t>Mesas VIP / clientes especiales:</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr"/>
+      <c r="C7" s="15" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="B8" s="8" t="inlineStr">
@@ -677,7 +768,7 @@
           <t>Grupos o eventos:</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr"/>
+      <c r="C8" s="15" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" s="8" t="inlineStr">
@@ -685,7 +776,7 @@
           <t>Ocupación estimada:</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>_____ %</t>
         </is>
@@ -706,7 +797,7 @@
           <t>Plato del día 1:</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr"/>
+      <c r="C12" s="15" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="B13" s="8" t="inlineStr">
@@ -714,7 +805,7 @@
           <t>Plato del día 2:</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr"/>
+      <c r="C13" s="15" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="B14" s="8" t="inlineStr">
@@ -722,7 +813,7 @@
           <t>Postre especial:</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr"/>
+      <c r="C14" s="15" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="B15" s="8" t="inlineStr">
@@ -730,7 +821,7 @@
           <t>Productos AGOTADOS (86):</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr"/>
+      <c r="C15" s="15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="B16" s="8" t="inlineStr">
@@ -738,7 +829,7 @@
           <t>Cambios en carta:</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr"/>
+      <c r="C16" s="15" t="inlineStr"/>
     </row>
     <row r="17"/>
     <row r="18">
@@ -755,7 +846,7 @@
           <t>Reservas con alérgenos declarados:</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr"/>
+      <c r="C19" s="15" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="B20" s="8" t="inlineStr">
@@ -763,7 +854,7 @@
           <t>Dietas especiales (vegano, celíaco...):</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr"/>
+      <c r="C20" s="15" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="B21" s="8" t="inlineStr">
@@ -771,7 +862,7 @@
           <t>Restricciones a comunicar:</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr"/>
+      <c r="C21" s="15" t="inlineStr"/>
     </row>
     <row r="22"/>
     <row r="23">
@@ -788,7 +879,7 @@
           <t>Personal cocina:</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr"/>
+      <c r="C24" s="15" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="B25" s="8" t="inlineStr">
@@ -796,7 +887,7 @@
           <t>Personal sala:</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr"/>
+      <c r="C25" s="15" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="B26" s="8" t="inlineStr">
@@ -804,7 +895,7 @@
           <t>Personal barra:</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr"/>
+      <c r="C26" s="15" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="B27" s="8" t="inlineStr">
@@ -812,7 +903,7 @@
           <t>¿Falta alguien? Cobertura:</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr"/>
+      <c r="C27" s="15" t="inlineStr"/>
     </row>
     <row r="28"/>
     <row r="29">
@@ -829,7 +920,7 @@
           <t>Incidencias del turno anterior:</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr"/>
+      <c r="C30" s="15" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="B31" s="8" t="inlineStr">
@@ -837,7 +928,7 @@
           <t>Objetivos del turno:</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr"/>
+      <c r="C31" s="15" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="B32" s="8" t="inlineStr">
@@ -845,7 +936,7 @@
           <t>Mensaje del manager:</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr"/>
+      <c r="C32" s="15" t="inlineStr"/>
     </row>
     <row r="33"/>
     <row r="34"/>
@@ -860,11 +951,12 @@
     <row r="37">
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>— Kit de Tareas Recurrentes · AI Chef Pro · aichef.pro</t>
+          <t>— Kit de Tareas Recurrentes · Restaurante Casual · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="6">
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B4:C4"/>

--- a/astro-site/public/dl/kit-tareas/BONUS-01-briefing-servicio.xlsx
+++ b/astro-site/public/dl/kit-tareas/BONUS-01-briefing-servicio.xlsx
@@ -622,10 +622,10 @@
       </c>
     </row>
     <row r="11"/>
-    <row r="12" ht="32" customHeight="1">
+    <row r="12" ht="16" customHeight="1">
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día (accesos, luces, clima, terraza).</t>
+          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día.</t>
         </is>
       </c>
     </row>
@@ -643,10 +643,10 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="16" customHeight="1">
+    <row r="15" ht="48" customHeight="1">
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>▸ Orden de uso: local → áreas → caja. No se duplican: cada uno cubre un nivel.</t>
+          <t>▸ Orden de uso: local → áreas → caja. Cada fichero cubre un nivel: el de negocio marca el HITO (encender, abrir, cerrar), el de áreas detalla CÓMO se hace en cada zona y el de caja lleva el DINERO. Si una tarea aparece en dos, es a propósito: una es el hito y la otra el detalle.</t>
         </is>
       </c>
     </row>
@@ -657,6 +657,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18" ht="18" customHeight="1">
       <c r="B18" s="13" t="inlineStr">
         <is>
@@ -664,6 +665,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20" ht="35" customHeight="1">
       <c r="B20" s="13" t="inlineStr">
         <is>
@@ -678,6 +680,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23" ht="18" customHeight="1">
       <c r="B23" s="13" t="inlineStr">
         <is>
@@ -706,7 +709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
